--- a/data/trans_dic/P02E$ssociales-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,31</t>
+          <t>1,01; 9,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,31</t>
+          <t>1,09; 6,06</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,6</t>
+          <t>1,28; 11,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,08</t>
+          <t>0,42; 4,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,55</t>
+          <t>0,61; 3,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,99</t>
+          <t>0,48; 4,06</t>
         </is>
       </c>
     </row>
@@ -898,32 +898,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,79</t>
+          <t>0,0; 9,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,54</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,77</t>
+          <t>0,96; 9,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 9,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,38</t>
+          <t>0,56; 5,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,25</t>
+          <t>1,37; 5,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,69</t>
+          <t>0,52; 4,61</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,39</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,38</t>
+          <t>0,0; 11,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,79</t>
+          <t>1,05; 8,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,61</t>
+          <t>1,28; 7,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 10,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 9,02</t>
+          <t>0,93; 8,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,7</t>
+          <t>0,52; 4,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,23</t>
+          <t>0,91; 5,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1468,27 +1468,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,46</t>
+          <t>0,3; 2,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,86</t>
+          <t>0,73; 2,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,67</t>
+          <t>0,16; 1,65</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,54</t>
+          <t>0,95; 2,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,46</t>
+          <t>0,67; 2,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,07</t>
+          <t>0,1; 1,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,96</t>
+          <t>0,81; 2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,7</t>
+          <t>0,48; 1,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,84</t>
+          <t>0,18; 0,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,99</t>
+          <t>1,01; 2,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,66</t>
+          <t>0,73; 1,72</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6056</t>
+          <t>0; 5533</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4860</t>
+          <t>0; 4789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2126</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5202</t>
+          <t>0; 5130</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1008; 9188</t>
+          <t>998; 9187</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2052</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6991</t>
+          <t>0; 7145</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1849; 10893</t>
+          <t>1882; 10456</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6650</t>
+          <t>0; 7304</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1011; 8471</t>
+          <t>1019; 9031</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6165</t>
+          <t>0; 6317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>999; 8663</t>
+          <t>885; 8720</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6264</t>
+          <t>0; 5862</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2128; 12131</t>
+          <t>2080; 11850</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1018; 8536</t>
+          <t>1019; 8695</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6118</t>
+          <t>0; 6878</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4569</t>
+          <t>0; 5528</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4513</t>
+          <t>0; 3876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4516</t>
+          <t>0; 5972</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1788</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6570</t>
+          <t>0; 6565</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 7189</t>
+          <t>0; 6989</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4609</t>
+          <t>0; 4858</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1928</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1052; 9747</t>
+          <t>1063; 10222</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5107</t>
+          <t>0; 5352</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1850</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1080; 9737</t>
+          <t>1013; 10454</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6945</t>
+          <t>0; 6919</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1893</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3248; 15319</t>
+          <t>4002; 15709</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932; 8333</t>
+          <t>930; 8187</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1847</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6806</t>
+          <t>0; 7024</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 7085</t>
+          <t>0; 6073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>971; 8122</t>
+          <t>971; 8054</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 4720</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6161</t>
+          <t>0; 6120</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1983; 11208</t>
+          <t>1885; 11024</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5617</t>
+          <t>0; 5476</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1964</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6705</t>
+          <t>0; 6603</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>990; 9931</t>
+          <t>1025; 9837</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5718</t>
+          <t>0; 5828</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>987; 9038</t>
+          <t>991; 8967</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8462</t>
+          <t>0; 8019</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5105</t>
+          <t>0; 4530</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7652</t>
+          <t>0; 7986</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5430</t>
+          <t>0; 4524</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 7018</t>
+          <t>0; 8119</t>
         </is>
       </c>
     </row>
@@ -3002,17 +3002,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2010</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1963; 10981</t>
+          <t>1902; 11178</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4806</t>
+          <t>0; 4329</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3022,27 +3022,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1066; 8789</t>
+          <t>1064; 8698</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 8789</t>
+          <t>0; 9136</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5834</t>
+          <t>0; 5335</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3917; 16237</t>
+          <t>4166; 15876</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>862; 9143</t>
+          <t>861; 9050</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 6502</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9290; 24976</t>
+          <t>9346; 26343</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5209; 18585</t>
+          <t>5085; 18973</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1878; 10719</t>
+          <t>1050; 10784</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12289; 29755</t>
+          <t>12338; 30853</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5172; 18929</t>
+          <t>5318; 19067</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2909; 13638</t>
+          <t>2875; 13372</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>25836; 49672</t>
+          <t>25363; 50094</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12635; 31076</t>
+          <t>13685; 32176</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Provincia-trans_dic.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 6,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,3</t>
+          <t>1,0; 9,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,06</t>
+          <t>1,09; 5,84</t>
         </is>
       </c>
     </row>
@@ -793,22 +793,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,3</t>
+          <t>1,25; 10,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,11</t>
+          <t>0,48; 4,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,47</t>
+          <t>0,61; 3,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,06</t>
+          <t>0,47; 4,48</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,88</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 5,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,19</t>
+          <t>0,88; 8,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,04</t>
+          <t>0,0; 8,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,78</t>
+          <t>0,6; 5,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,38</t>
+          <t>1,39; 5,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,61</t>
+          <t>0,53; 4,53</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>0,0; 13,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,47</t>
+          <t>0,0; 11,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,71</t>
+          <t>1,05; 8,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,48</t>
+          <t>1,29; 7,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,52</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,93</t>
+          <t>0,93; 8,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,67</t>
+          <t>0,52; 5,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,32</t>
+          <t>0,95; 5,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,44</t>
+          <t>0,3; 2,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,8</t>
+          <t>0,7; 2,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,65</t>
+          <t>0,16; 1,72</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,67</t>
+          <t>1,0; 2,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,51</t>
+          <t>0,66; 2,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,03</t>
+          <t>0,79; 1,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,72</t>
+          <t>0,45; 1,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,82</t>
+          <t>0,17; 0,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,0</t>
+          <t>1,02; 1,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,72</t>
+          <t>0,7; 1,75</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5533</t>
+          <t>0; 5411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4789</t>
+          <t>0; 4893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5130</t>
+          <t>0; 5046</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>998; 9187</t>
+          <t>988; 9810</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7145</t>
+          <t>0; 6598</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1882; 10456</t>
+          <t>1886; 10077</t>
         </is>
       </c>
     </row>
@@ -2029,22 +2029,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7304</t>
+          <t>0; 6437</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1019; 9031</t>
+          <t>1003; 8634</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6317</t>
+          <t>0; 5413</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>885; 8720</t>
+          <t>1015; 8621</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5862</t>
+          <t>0; 5391</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2080; 11850</t>
+          <t>2091; 11020</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1019; 8695</t>
+          <t>1014; 9579</t>
         </is>
       </c>
     </row>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6878</t>
+          <t>0; 5664</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5528</t>
+          <t>0; 5093</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>0; 4597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5972</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2217,17 +2217,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6565</t>
+          <t>0; 6534</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 6989</t>
+          <t>0; 7408</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4858</t>
+          <t>0; 5047</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1063; 10222</t>
+          <t>978; 9329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5352</t>
+          <t>0; 5162</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1013; 10454</t>
+          <t>1082; 10229</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6919</t>
+          <t>0; 7066</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4002; 15709</t>
+          <t>4047; 15806</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>930; 8187</t>
+          <t>938; 8053</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7024</t>
+          <t>0; 7581</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2528,32 +2528,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6073</t>
+          <t>0; 6183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>971; 8054</t>
+          <t>975; 8269</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4720</t>
+          <t>0; 5961</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6120</t>
+          <t>0; 7062</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1885; 11024</t>
+          <t>1906; 10598</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5476</t>
+          <t>0; 4833</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6603</t>
+          <t>0; 7841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1025; 9837</t>
+          <t>1021; 9027</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5828</t>
+          <t>0; 5994</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>991; 8967</t>
+          <t>999; 9989</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8019</t>
+          <t>0; 7703</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7986</t>
+          <t>0; 6650</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 4187</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 8119</t>
+          <t>0; 7543</t>
         </is>
       </c>
     </row>
@@ -3007,42 +3007,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1902; 11178</t>
+          <t>2000; 11452</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4329</t>
+          <t>0; 3523</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 5273</t>
+          <t>0; 5339</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1064; 8698</t>
+          <t>1067; 9882</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 9136</t>
+          <t>0; 7543</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5335</t>
+          <t>0; 6137</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4166; 15876</t>
+          <t>3969; 16413</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>861; 9050</t>
+          <t>864; 9404</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 6502</t>
+          <t>0; 6168</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9346; 26343</t>
+          <t>9871; 25870</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5085; 18973</t>
+          <t>5009; 19007</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1050; 10784</t>
+          <t>1897; 11091</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12338; 30853</t>
+          <t>12014; 29190</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5318; 19067</t>
+          <t>5034; 18590</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2875; 13372</t>
+          <t>2810; 13528</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>25363; 50094</t>
+          <t>25513; 49172</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>13685; 32176</t>
+          <t>12998; 32692</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
